--- a/sample_docs/corpus_v2/harim/harim_15_협력농가위생점검일정표.xlsx
+++ b/sample_docs/corpus_v2/harim/harim_15_협력농가위생점검일정표.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,6 +527,20 @@
       </c>
       <c r="D5" s="1" t="n">
         <v>46414</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>※ 점검은 품질안전팀이 방문하여 실시하며, 일정 변경은 1주 전까지 농가에 통보한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>※ 점검 결과 부적합 판정을 받은 농가는 30일 안에 개선 계획서를 제출한다.</t>
+        </is>
       </c>
     </row>
   </sheetData>
